--- a/samples/수주취합/2026.09.29_납품예정 안산AM.xlsx
+++ b/samples/수주취합/2026.09.29_납품예정 안산AM.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="66">
   <si>
     <t>품목코드</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>NB(일반)</t>
+  </si>
+  <si>
+    <t>KRW</t>
   </si>
   <si>
     <t>NB</t>
@@ -795,11 +798,11 @@
       <c r="K2" t="s">
         <v>55</v>
       </c>
-      <c r="L2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M2" t="s">
-        <v>55</v>
+      <c r="L2">
+        <v>2500</v>
+      </c>
+      <c r="M2">
+        <v>12500</v>
       </c>
       <c r="N2" t="s">
         <v>55</v>
@@ -853,7 +856,7 @@
         <v>55</v>
       </c>
       <c r="AE2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="AF2" t="s">
         <v>55</v>
@@ -907,7 +910,7 @@
         <v>55</v>
       </c>
       <c r="AW2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AX2" t="s">
         <v>55</v>
@@ -924,10 +927,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
         <v>55</v>
@@ -951,16 +954,16 @@
         <v>46300.000601851854</v>
       </c>
       <c r="J3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K3" t="s">
         <v>55</v>
       </c>
-      <c r="L3" t="s">
-        <v>55</v>
-      </c>
-      <c r="M3" t="s">
-        <v>55</v>
+      <c r="L3">
+        <v>2700</v>
+      </c>
+      <c r="M3">
+        <v>2700</v>
       </c>
       <c r="N3" t="s">
         <v>55</v>
@@ -1008,13 +1011,13 @@
         <v>55</v>
       </c>
       <c r="AC3" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD3" t="s">
         <v>55</v>
       </c>
       <c r="AE3" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="AF3" t="s">
         <v>55</v>
@@ -1068,7 +1071,7 @@
         <v>55</v>
       </c>
       <c r="AW3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AX3" t="s">
         <v>55</v>
